--- a/12609198.xlsx
+++ b/12609198.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6f77ca67a4eaafc/Pictures/Desktop/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56CF4CEC-C1C2-416E-B9C2-439769E55123}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFD87EAD-F214-4BB7-B52C-90F99E77FBF2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,54 @@
   </si>
   <si>
     <t>spend quality time with friends</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I went to the market for shopping </t>
+  </si>
+  <si>
+    <t>relaxed at hostel and watched a movie.</t>
+  </si>
+  <si>
+    <t>spent the evening playing football</t>
+  </si>
+  <si>
+    <t>struggled to focus after afternoon.</t>
+  </si>
+  <si>
+    <t>had an excellent dinner with friends.</t>
+  </si>
+  <si>
+    <t>feel unmotivated today.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm struggling to find the motivation to go to class after the  weekend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was preparing for CA </t>
+  </si>
+  <si>
+    <t>feel lazy.</t>
+  </si>
+  <si>
+    <t>today's class was interesting .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">listened to music while doing light chores </t>
+  </si>
+  <si>
+    <t xml:space="preserve">did not sleep well last night </t>
+  </si>
+  <si>
+    <t>felt sluggish all day</t>
+  </si>
+  <si>
+    <t>took rest day to recharge.</t>
+  </si>
+  <si>
+    <t>I woke up with full energy.</t>
   </si>
 </sst>
 </file>
@@ -903,7 +951,9 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="6" width="11" customWidth="1"/>
+    <col min="2" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -1073,7 +1123,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>46255</v>
       </c>
@@ -1117,7 +1167,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>46256</v>
       </c>
@@ -1381,7 +1431,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46261</v>
       </c>
@@ -1469,423 +1519,879 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B16" s="14">
+        <v>420</v>
+      </c>
+      <c r="C16" s="14">
+        <v>45</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>795</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>645</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>45</v>
+      </c>
+      <c r="D17" s="14">
+        <v>240</v>
+      </c>
+      <c r="E17" s="14">
+        <v>120</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>200</v>
+      </c>
+      <c r="G19" s="14">
+        <v>4</v>
+      </c>
+      <c r="H19" s="14">
+        <v>30</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>400</v>
+      </c>
+      <c r="G20" s="14">
+        <v>8</v>
+      </c>
+      <c r="H20" s="14">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>200</v>
+      </c>
+      <c r="G21" s="14">
+        <v>4</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1015</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>425</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>45</v>
+      </c>
+      <c r="D23" s="14">
+        <v>240</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>90</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>45</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>90</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>45</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>90</v>
+      </c>
+      <c r="F25" s="14">
+        <v>360</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>345</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>90</v>
+      </c>
+      <c r="E26" s="14">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14">
+        <v>240</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>30</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
+      <c r="F27" s="14">
+        <v>480</v>
+      </c>
+      <c r="G27" s="14">
+        <v>8</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>90</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>240</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>120</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>30</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>45</v>
+      </c>
+      <c r="D30" s="14">
+        <v>240</v>
+      </c>
+      <c r="E30" s="14">
+        <v>90</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+        <v>585</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>45</v>
+      </c>
+      <c r="D31" s="14">
+        <v>240</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>30</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>585</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>45</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>360</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>30</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>375</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B33" s="14">
+        <v>420</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>180</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
+      <c r="F33" s="14">
+        <v>240</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>30</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>45</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>90</v>
+      </c>
+      <c r="F34" s="14">
+        <v>480</v>
+      </c>
+      <c r="G34" s="14">
+        <v>8</v>
+      </c>
+      <c r="H34" s="14">
+        <v>30</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>195</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/12609198.xlsx
+++ b/12609198.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6f77ca67a4eaafc/Pictures/Desktop/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFD87EAD-F214-4BB7-B52C-90F99E77FBF2}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6846405-AD05-44BC-BB68-4ADA707803E2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2394,21 +2394,25 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
+      <c r="A35" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B35" s="14">
+        <v>360</v>
+      </c>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>360</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
@@ -2416,7 +2420,9 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13">
+        <v>46283</v>
+      </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -2438,7 +2444,9 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13">
+        <v>46284</v>
+      </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -2460,7 +2468,9 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46285</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -2482,7 +2492,9 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
+      <c r="A39" s="13">
+        <v>46286</v>
+      </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>

--- a/12609198.xlsx
+++ b/12609198.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6f77ca67a4eaafc/Pictures/Desktop/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6846405-AD05-44BC-BB68-4ADA707803E2}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{466F17D0-E081-489A-844A-3E1434323940}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="132" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,18 @@
   </si>
   <si>
     <t>I woke up with full energy.</t>
+  </si>
+  <si>
+    <t>I went to the uni mall .</t>
+  </si>
+  <si>
+    <t>excited for the weekend</t>
+  </si>
+  <si>
+    <t>I woke up earler</t>
+  </si>
+  <si>
+    <t>work on minor project</t>
   </si>
 </sst>
 </file>
@@ -2417,7 +2429,9 @@
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+      <c r="N35" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
@@ -2441,7 +2455,9 @@
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+      <c r="N36" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
@@ -2465,7 +2481,9 @@
       <c r="K37" s="16"/>
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="N37" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
@@ -2489,7 +2507,9 @@
       <c r="K38" s="16"/>
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="N38" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
@@ -2513,7 +2533,9 @@
       <c r="K39" s="16"/>
       <c r="L39" s="16"/>
       <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="N39" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
